--- a/통합 문서1.xlsx
+++ b/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\weather_prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDC9D747-1846-403B-977B-F77DB860433A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF88318D-3109-4768-9061-B30B0042C311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{24E3AD02-5F98-4F36-91AE-A445CFE4CEA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{24E3AD02-5F98-4F36-91AE-A445CFE4CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +452,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,7 +537,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -553,9 +559,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -569,6 +572,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -911,7 +920,7 @@
     <col min="1" max="4" width="25.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -925,7 +934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -939,7 +948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -953,11 +962,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -967,35 +976,35 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -1005,29 +1014,29 @@
       <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1037,7 +1046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1051,7 +1060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -1065,11 +1074,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1079,7 +1088,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
@@ -1093,11 +1102,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1107,7 +1116,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1121,11 +1130,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1135,21 +1144,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -1163,11 +1172,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1177,21 +1186,21 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>78</v>
       </c>
@@ -1205,25 +1214,25 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -1233,53 +1242,53 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1289,7 +1298,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>106</v>
       </c>
@@ -1303,7 +1312,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>110</v>
       </c>
